--- a/docs/downloads/20260823_Johor_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/20260823_Johor_Teduh_Weekly_Update.xlsx
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AI8" s="10" t="inlineStr">
         <is>
-          <t>Latest sales - Block A: 48</t>
+          <t>Open sale for Block A (416 units) only; tracked against the full development</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AI12" s="10" t="inlineStr">
         <is>
-          <t>Latest sales - Block A: 449, Block B1: 231, Block B2: 285, Block D1: 168, Block D2: 288</t>
+          <t>Open sale for Block A, B &amp; D only. Block C (833 units) is not opened yet. Latest sales - Block A: 449, Block B1: 231, Block B2: 285, Block D1: 168, Block D2: 288</t>
         </is>
       </c>
     </row>
